--- a/2026纽约首尔旅行深度优化行程计划.xlsx
+++ b/2026纽约首尔旅行深度优化行程计划.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3256,7 +3256,7 @@
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Day 8 · 10/09 (周五) ｜ 汉南洞晨咖 ➔ Leeum 美术馆 ➔ 汉南洞设计师买手街 ➔ 乐天总店 &amp; Olive Young 明洞 ➔ 德寿宫石墙路 ➔ 王妃家烤肉 ｜ 🏨 酒店：Nine Tree Premier Hotel Insadong ｜ ☀️ 首尔日落 18:01 ｜ 🎨 首尔美学潮流日：先锋艺术、顶级买手、明洞免税与秋日最美宫墙</t>
+          <t>Day 8 · 10/09 (周五) ｜ 德寿宫/市政厅外貌 ➔ 乐天百货(星光大道/GM/9F女装) ➔ Coin Cafe/Acorn画像/Emis/Rockfish/nyunyu/Fun Road ➔ 江南狎鸥亭(Tamburins Jennie墙/Vivaia/Woody zip/empty/kasina/Human made/Worksout/mooni/kossette) ➔ 新沙(Tamburins/ADER error) ➔ 元祖马山酱蟹 ➔ 盘浦汉江公园喷泉 ｜ 🏨 酒店：Nine Tree Premier Hotel Insadong (首尔九树仁寺洞) ｜ ☀️ 首尔日落 18:01 ｜ 🛍️ 首尔第一天：明洞核心扫货 + 跨江江南(狎鸥亭&amp;新沙) + 盘浦汉江公园彩虹喷泉水舞</t>
         </is>
       </c>
       <c r="B57" s="3" t="n"/>
@@ -3269,7 +3269,7 @@
       <c r="I57" s="3" t="n"/>
       <c r="J57" s="3" t="n"/>
     </row>
-    <row r="58" ht="36" customHeight="1">
+    <row r="58" ht="52" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Day 8</t>
@@ -3287,22 +3287,22 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Milestone Coffee (汉南洞店)</t>
+          <t>德寿宫大汉门 &amp; 市政厅外貌巡礼</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>清晨前往汉南洞静谧山坡，在新沙洞红到汉南洞的人气精品咖啡馆小坐。红砖庭院、露天木质窗台，品尝首尔天花板级维也纳咖啡。</t>
+          <t>清晨向南漫步来到德寿宫前广场。打卡大汉门宏伟宫门与被誉为首尔最浪漫散步道的贞洞石墙路外貌；移步对街欣赏首尔新旧市政厅交相辉映的波浪流线玻璃建筑与古典石砌老建筑。</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>☕ 招牌必点：Einspänner 维也纳鲜奶油冰咖啡、手工现烤提拉米苏 (Tiramisu)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>🚕 酒店打车至汉南洞约 12 分钟，或地铁 6 号线汉江镇站 1 号出口</t>
+          <t>🚶 从九树酒店向南步行 10 分钟跨过清溪川即达市厅广场</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>清晨人流稀少，石墙路两侧秋叶金黄，是拍摄无杂质街景的黄金时段。</t>
         </is>
       </c>
     </row>
@@ -3344,14 +3344,16 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Leeum 三星美术馆 (Leeum Museum of Art)</t>
+          <t>乐天百货总店 (1F星光大道 ➔ B1美食 ➔ 3F GM ➔ 9F韩系女装大本营)</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>探访由马里奥·博塔、让·努维尔和雷姆·库哈斯三位世界级建筑大师联手设计的先锋艺术地标。
-• Museum 1 传统艺术馆：白色旋转天窗圆楼梯是首尔最著名的建筑打卡点
-• Museum 2 现代与当代艺术馆：近距离观赏贾科梅蒂、罗斯科、安尼施·卡普尔等大师杰作</t>
+          <t>步入乐天百货总店开启高效率集中扫货：
+• 1F 星光大道 (Star Avenue)：打卡韩流明星手印长廊与巨幅环绕互动光影屏；
+• B1 食品精品馆：选购传统高丽参糖、海苔礼盒与特色点心；
+• 3F Gentle Monster：试戴最新款黑超墨镜与光学眼镜；
+• 9F 本土设计师女装大本营：手绘图力荐层！集中收录 Coyseio、Matin Kim、Mardi Mercredi、Tree Ming Bird 等全网顶流好牌，一站式购齐免去四处奔波！</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -3361,21 +3363,21 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>🎟️ 提前于官网预约常设展入场资格（常设展免费参观）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>🚶 从 Milestone Coffee 沿梨泰院路 55 街步行 3 分钟即达美术馆正门</t>
+          <t>🚶 沿小公路步行 5 分钟直达乐天百货乙支路入口</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="36" customHeight="1">
+          <t>9 楼汇集了首尔最火的平价与设计师潮牌，现场支持即时退税，购物效率极高！</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="52" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Day 8</t>
@@ -3393,22 +3395,28 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Solgot Hannam (汉南洞精致传统釜饭)</t>
+          <t>明洞核心潮流探店 &amp; Fun Road 漫画街 (Coin Cafe / Acorn画像 / Emis / Rockfish / nyunyu)</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>享用首尔当下极具人气的现代传统韩式石锅釜饭。新鲜牛排、鲍鱼、香菇在铸铁锅中慢火焖煮，搭配香脆锅巴茶汤。</t>
+          <t>漫步明洞步行街核心巷弄：
+• Cafe Coin 明洞店：在三十年老牌复古木质咖啡馆小憩，品尝经典手冲咖啡与华夫饼；
+• Acorn Caricature：在一分钟内现场绘制俏皮复古黑白人像漫画头像；
+• Emis 明洞旗舰店：抢购经典刺绣字母棒球帽与印花托特包；
+• Rockfish Weatherwear：选购英伦风复古玛丽珍鞋与芭蕾舞平底鞋；
+• nyunyu myeongdong：三层饰品长廊挑选潮流耳饰发饰；
+• Fun Road 趣味路漫画街：沿明洞站向南山方向漫步，欣赏生动有趣的漫画墙绘与雕塑。</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>🍲 推荐：特选牛排釜饭 (Steak Kamameshi)、鲜鲍鱼釜饭，清香回甘</t>
+          <t>☕ Cafe Coin：招牌维也纳咖啡 (Einspanner) / 水果比利时华夫饼</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -3418,12 +3426,12 @@
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>🚶 从 Leeum 美术馆步行 5 分钟至汉南洞核心小巷</t>
+          <t>🚶 明洞步行街各店铺步行均在 2-3 分钟内</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Emis 热门色棒球帽上午补货最全；nyunyu 满额现场退税。</t>
         </is>
       </c>
     </row>
@@ -3445,27 +3453,31 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>汉南洞设计师买手街 (Itaewon-ro 54-gil)</t>
+          <t>跨江前往江南：狎鸥亭岛山公园潮流矩阵 (Tamburins Jennie墙 / Vivaia / Woody zip / empty / kasina / Human made / Worksout / mooni / kossette)</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>深度漫步首尔当下最精致的设计师品牌街区。
-• Mardi Mercredi（经典小雏菊刺绣卫衣与针织衫旗舰店）
-• Rest &amp; Recreation（R&amp;R 先锋剪裁潮牌）
-• Grove Store（格罗夫法式复古名媛风）
-• Rockfish Weatherwear（英伦芭蕾风单鞋与玛丽珍鞋）
-• Nonfiction &amp; TAMBURINS 汉南香氛艺术空间</t>
+          <t>搭乘地铁跨越汉江步入首尔奢华潮流心脏——狎鸥亭罗德奥与岛山公园：
+• Tamburins HAUS DOSAN：打卡外墙超巨幅 Jennie 艺术照片大片墙，进店体验室内动力学巨型装置与香氛蛋；
+• Vivaia 鞋店：选购舒适轻盈的环保针织鞋履；
+• Woody zip (utmost)：探索独立小众设计师服饰；
+• empty 买手店：极简工业风空间选购先锋设计师时装；
+• kasina 1997：打卡韩国球鞋潮流文化发源名所；
+• Human Made Seoul：打卡 NIGO 经典标志性日潮概念店；
+• Worksout 旗舰：精选欧美日韩高端街头工装；
+• Cafe Mooni 或 Queen's Park：在拥有粉色梦幻旋转大门的 Mooni 露台品尝下午茶，或在 Queen's Park 享用英式甜点；
+• Cafe Kossette：打卡门口出片率极高的小众咖啡馆门头拍照。</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🍰 Cafe Mooni：招牌蝴蝶结特调拿铁 + 粉色手工马卡龙蛋糕</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -3475,12 +3487,12 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🚇 明洞乘 4 号线至忠武路转 3 号线至狎鸥亭站 (Apgujeong) 3 号出口，步行约 8 分钟进入岛山公园街区</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>许多小店支持现场即时免税退税，随身携带护照原件</t>
+          <t>岛山公园周边被誉为首尔审美最高峰，街拍氛围极浓，偶遇演艺名流几率极高。</t>
         </is>
       </c>
     </row>
@@ -3502,19 +3514,19 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>乐天百货总店免税店 &amp; Olive Young 明洞全球旗舰店</t>
+          <t>新沙洞林荫道漫步 (Tamburins 新沙 ➔ ADER Space 新沙)</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>乘车返回市中心开启美妆免税采购。
-• 乐天百货 9-12F 免税店集中采购大牌护肤品与烟酒
-• 前往 Olive Young 明洞 Town 全球旗舰店：双层超大空间，韩国本土小众爆款面膜、防晒、精华一站式买齐并享受店内即时退税</t>
+          <t>向西南漫步至新沙洞林荫道（Garosu-gil）：
+• Tamburins 新沙旗舰店：探访独栋艺术概念展厅，感受不同于岛山公园的另一重香氛美学空间；
+• ADER Space 新沙旗舰店：打卡超震撼的太空舱与超时空概念艺术装置，选购解构主义廓形连帽衫与配饰。</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -3529,16 +3541,16 @@
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>🚕 汉南洞打车穿越南山隧道直达明洞约 12 分钟</t>
+          <t>🚶 从岛山公园向西南漫步约 12 分钟即达新沙洞林荫道</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="36" customHeight="1">
+          <t>ADER Space 进店如同穿梭未来艺术馆，每层均设有不同的科幻互动空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="52" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Day 8</t>
@@ -3556,22 +3568,22 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>德寿宫贞洞石墙路 (Deoksugung Stonewall Walkway)</t>
+          <t>晚餐：元祖马山酱蟹 &amp; 辣炖安康鱼老店</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>初秋黄昏漫步于被评为“韩国最美小路”的德寿宫石墙林荫道。红黄交织的银杏枫叶映衬着古典青瓦石墙，浪漫宁静，首尔散步天花板。</t>
+          <t>前往新沙洞著名的酱蟹美食街，步入传承数十载的元祖马山老店。品尝满黄生腌梭子蟹——蟹肉晶莹剔透如果冻般鲜美，将浓郁蟹黄与热腾腾的米饭、海苔碎和香油拌入蟹壳中大快朵颐（韩国正统「偷饭贼」美味）；同时品尝热辣鲜甜的招牌辣炖安康鱼！</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🦀 招牌盛宴：顶级满黄特大酱油腌蟹 (Ganjang Gejang) + 辣炖安康鱼 (Agujjim) + 蟹黄拌饭</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -3581,16 +3593,16 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>🚶 从明洞乐天总店向西步行 6 分钟至首尔市厅与德寿宫大门</t>
+          <t>🚶 从林荫道步行 4 分钟即达新沙站 4 号出口附近酱蟹街</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="36" customHeight="1">
+          <t>周六晚间人气极旺，鲜美无腥味，是首尔必吃的美食巅峰体验之一。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="52" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Day 8</t>
@@ -3608,22 +3620,22 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>王妃家精品烤肉 (WangBiJip 明洞/钟路总店)</t>
+          <t>盘浦汉江公园 (月光彩虹喷泉水舞表演)</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>首尔极负盛名的炭火烤肉名店。全程由专业店员炭火代烤，火候锁汁恰到好处，无需自己动手。</t>
+          <t>晚餐后搭乘出租车前往盘浦汉江公园。夜幕降临，倚靠在江畔台阶上，观赏吉尼斯世界纪录最长的「月光彩虹喷泉」（周六晚 20:00 / 20:30 每场喷水表演 20 分钟）。近 400 个喷头随着世界名曲与流行音乐喷射出绚丽七彩水柱，在初秋汉江晚风中欣赏对岸南山首尔塔璀璨夜景。</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>🥩 必尝招牌：农协特选优质韩牛里脊、秘制酱汁调味烤牛排肉、海鲜泡菜煎饼配爽口水冷面</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
@@ -3633,12 +3645,12 @@
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>🚶 从德寿宫漫步或打车 5 分钟即达</t>
+          <t>🚕 从新沙洞打车直达盘浦汉江公园潜水桥（车程约 8 分钟，预算约 6,000 韩元）</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>秋夜江边微风徐徐，带一件薄外套防风；现场许多市民在草坪野餐，气氛悠闲治愈。</t>
         </is>
       </c>
     </row>
@@ -3660,17 +3672,17 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>漫步返回九树酒店休整</t>
+          <t>返回九树仁寺洞酒店休整</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>带着丰富的战利品步行返回九树仁寺洞酒店，整理美妆行李，享受舒适客房设施。</t>
+          <t>从盘浦汉江公园搭乘出租车或地铁穿过汉江大桥返回中区九树酒店，卸下战利品，享受热水澡，安然休息。</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -3685,7 +3697,7 @@
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>🚶 步行 5 分钟回酒店</t>
+          <t>🚕 打车返回九树仁寺洞酒店（约 20 分钟，约 12,000 韩元）</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr">
@@ -3697,7 +3709,7 @@
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Day 9 · 10/10 (周六) ｜ 弘大延南洞晨漫 ➔ 梨花女大地下峡谷 ➔ 跨城江南狎鸥亭 ➔ 岛山公园潮流矩阵 ➔ 📌 名人里脊 1++ 纯血熟成韩牛 ｜ 🏨 酒店：Nine Tree Premier Hotel Insadong ｜ ☀️ 首尔日落 18:00 ｜ 🥩 潮流先锋与舌尖奢享：青春西区校园，江南名媛圣地，殿堂级纯血韩牛</t>
+          <t>Day 9 · 10/10 (周六) ｜ Leeum三星美术馆 ➔ 汉南洞先锋买手(Hince/Glowny/R&amp;R/anoetic) ➔ 韩国部队锅午餐 ➔ open yy/Elborn ➔ Passion 5下午茶 ➔ 梨泰院解放村Urban Cliff日落 ➔ 新兴市场小吃 ➔ 108阶梯 ｜ 🏨 酒店：Nine Tree Premier Hotel Insadong (首尔九树仁寺洞) ｜ ☀️ 首尔日落 17:59 ｜ 🎨 首尔第二天：汉南洞美学漫步(Leeum美术馆&amp;先锋买手&amp;部队锅) + 梨泰院解放村Urban Cliff绝美落日</t>
         </is>
       </c>
       <c r="B66" s="3" t="n"/>
@@ -3710,7 +3722,7 @@
       <c r="I66" s="3" t="n"/>
       <c r="J66" s="3" t="n"/>
     </row>
-    <row r="67" ht="36" customHeight="1">
+    <row r="67" ht="52" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Day 9</t>
@@ -3728,17 +3740,17 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>弘大延南洞京义线林荫道 (Yeonnam-dong)</t>
+          <t>Leeum 三星美术馆 (周一闭馆)</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>周六清晨探访延南洞。废弃铁路改建的绿色林道两侧藏满了独立文创买手店、设计师杂货铺与复古唱片店，避开午后拥挤人群感受清新文艺气息。</t>
+          <t>前往汉南洞半山腰开启韩国艺术殿堂之旅。打卡世界级建筑大师 Mario Botta 与 Jean Nouvel 设计的现代建筑群。欣赏标志性纯白旋转楼梯天窗倒影、传统国宝青瓷与当代前卫装置艺术。</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -3748,21 +3760,21 @@
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>常设展免费，需提前 14 天在 Leeum 官网实名预约入场时段</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>🚇 酒店乘地铁 1 号线转 2 号线至弘大入口站 3 号出口</t>
+          <t>🚇 酒店乘地铁 3 号线至药水站转 6 号线至汉江镇站 (Hangangjin) 1 号出口，步行 6 分钟即达</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="36" customHeight="1">
+          <t>公休日照常开放（每周一固定闭馆，因此特意排在周五！）。馆内拍照极其出片，建议预留 1.5 小时。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="52" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Day 9</t>
@@ -3780,22 +3792,26 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Oats Coffee (延南洞胡同店)</t>
+          <t>汉南洞先锋买手街区 (Hince ➔ Glowny ➔ R&amp;R ➔ anoetic)</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>藏匿在延南洞安静住宅街角的人气咖啡馆。木质原木桌椅与小庭院，享受首尔招牌维也纳奶盖与现烘咖啡豆香。</t>
+          <t>漫步汉南洞高低错落的优雅街巷，集中打卡四大当红本土设计师品牌：
+• Hince 汉南洞旗舰店：清透水光美妆体验空间，试用当季果冻唇釉与水光气垫；
+• Glowny Hannam：复古芭蕾风少女感设计师女装，质感针织与丝绒裙装；
+• Rest &amp; Recreation (R&amp;R)：极简舒适休闲潮流单品与标志性圆环卫衣；
+• anoetic 汉南洞：小众先锋皮具手袋与高级感五金配饰。</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>☕ 必尝：招牌 Einspänner 维也纳咖啡、手工黄油司康</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
@@ -3805,16 +3821,16 @@
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>🚶 从林荫道漫步 4 分钟穿入延南小巷</t>
+          <t>🚶 从 Leeum 美术馆沿 Itaewon-ro 54-gil 顺坡漫步即达各专卖店</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="36" customHeight="1">
+          <t>各买手店相距仅数十米，红砖外立面与大面积玻璃落地窗极具视觉美感。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="52" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
           <t>Day 9</t>
@@ -3832,22 +3848,22 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>弘大核心潮流商圈 (Hongdae / ADER error)</t>
+          <t>午餐：Hannam Budaejjigae 韩国部队锅</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>漫步至弘大主街区。参观韩国顶尖潮流设计品牌 ADER error 弘大旗舰店的太空装置艺术空间，感受充满奇思妙想的概念陈列。</t>
+          <t>步入汉南洞多年老饕排队的传统老店 Hannam Budaejjigae 享用暖心午餐。香浓牛骨高汤中炖煮丰富午餐肉、维也纳香肠、年糕、泡菜与辛拉面，顶部铺上一片融化的金黄芝士，汤头浓郁微辣开胃！</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🍲 招牌必点：特制双份芝士部队锅 (Budae Jjigae) + 农心辛拉面组合</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
@@ -3857,16 +3873,16 @@
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>🚶 从延南洞穿过弘大站地下通道漫步至弘大西桥洞</t>
+          <t>🚶 位于买手街核心胡同内，步行 2 分钟即达</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="36" customHeight="1">
+          <t>大火煮沸后先吃拉面与午餐肉，汤汁拌米饭极其过瘾，全天漫步最佳能量补给。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="52" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
           <t>Day 9</t>
@@ -3884,22 +3900,25 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>新村地道午餐：百年参鸡汤 / 春川辣炒鸡排</t>
+          <t>汉南洞午后漫逛 (open yy ➔ Elborn) &amp; 奢华下午茶 (Passion 5 / Oasis Cafe)</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>在弘大与新村交界享用地道韩式午餐，热气腾腾的铁板鸡排炒年糕芝士，元气满满。</t>
+          <t>午后继续探索汉南洞高阶时尚与奢华甜品：
+• open yy (Open YY)：打卡当红前卫复古街头女装首尔旗舰店，选购限定款工装裙与印花 T 恤；
+• Elborn 汉南洞：漫步至极简法式优雅女装精品空间；
+• 下午茶享受：移步至 Passion 5 奢华法式甜品烘焙宫殿，在水滴旋转楼梯旁品尝手工千层酥与精致果挞；或在 Oasis Cafe 绿植花园庭院品尝现烤松饼与果汁。</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>🍗 推荐：春川辣炒鸡排加双份马苏里拉芝士与乌冬面</t>
+          <t>🍰 Passion 5：草莓鲜奶油蛋糕 / 招牌香草千层酥 (Mille-feuille) + 现磨手冲黑咖啡</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -3909,12 +3928,12 @@
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🚶 沿汉南大道向汉江镇站方向漫步约 5 分钟</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Passion 5 甜品陈列如珠宝展柜般璀璨，若想享受露天微风亦可选择 Oasis Cafe。</t>
         </is>
       </c>
     </row>
@@ -3936,22 +3955,25 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>梨花女子大学 (Ewha Womans University)</t>
+          <t>梨泰院解放村落日 (Urban Cliff) ➔ 新兴市场小吃 ➔ 108阶梯</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>探访韩国历史最悠久的女子名校。打卡由法国著名建筑师多米尼克·佩罗设计的标志性“大峡谷”下沉式多功能复合建筑 ECC（Ewha Campus Complex），红叶掩映下的哥特复兴大礼堂与现代地景建筑完美交融。</t>
+          <t>傍晚搭车前往梨泰院解放村（Sinheung-dong）山顶坡地：
+• Urban Cliff 梨泰院日落 (17:00)：登上全首尔公认日落景观第一的半山腰悬崖露台，点一杯特调气泡饮，正对金色夕阳下的南山首尔塔与漫山遍野的老城灯火（18:01 日落）；
+• Sinheung Market (新兴市场)：穿过复古拱廊天棚，打卡新兴艺术菜市场，探索地道小吃与潮流酒吧；
+• 108 steps (解放村 108 阶梯)：漫步至充满老首尔市井风情的 108 阶梯，体验沿坡攀升的斜行观光电梯，俯瞰坡地胡同交错的纵深街景。</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🍢 新兴市场地道小吃：炭烤五花肉串、韩式炸年糕与手作精酿生啤</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
@@ -3961,12 +3983,12 @@
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>🚇 地铁 2 号线乘 1 站至梨大站 2/3 号出口</t>
+          <t>🚕 汉南洞打车直达解放村五岔路口 / Urban Cliff（车程约 10 分钟，预算约 7,000 韩元）</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>日落前后半小时天色由粉紫转为深蓝，首尔塔亮起璀璨灯光，是首尔最具电影感的时刻！</t>
         </is>
       </c>
     </row>
@@ -3988,17 +4010,17 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>跨江前往江南狎鸥亭罗德奥 (Apgujeong Rodeo)</t>
+          <t>返回九树仁寺洞酒店休整</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>搭乘出租车跨越汉江，直奔江南最顶级的名媛与时尚发源地狎鸥亭罗德奥街区，两旁豪车穿梭，名店林立。</t>
+          <t>打车或乘地铁轻松返回仁寺洞九树酒店，在大堂整理白天的战利品，放松双腿，舒心就寝备战明日江南之行。</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
@@ -4013,7 +4035,7 @@
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>🚕 梨大直接打车经汉江大桥前往狎鸥亭罗德奥，约 25 分钟</t>
+          <t>🚕 从解放村打车返回九树酒店（约 15 分钟，约 10,000 韩元），或乘绿巴士转地铁</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
@@ -4022,179 +4044,179 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="52" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>Day 9</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>10/10 (周六)</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Day 10 · 10/11 (周日) ｜ London Bagel取号 ➔ 北村韩屋晨拍 ➔ Caffe del cotone ➔ Le Labo韩屋店/Tout Y Est ➔ 景福宫 ➔ 土俗村参鸡汤 ➔ 西村慢步(ofr/little tempo/one more bag/regins) ➔ 下午茶(PHAL/Camel/Namusae) ➔ 晚餐(神洞宫/两门烤肉/武桥洞明太鱼) ｜ 🏨 酒店：Nine Tree Premier Hotel Insadong (首尔九树仁寺洞) ｜ ☀️ 首尔日落 17:58 ｜ 🏯 古韵慢生活日：清晨避开人潮取号晨拍，历史宫殿与西村独立文艺街区慢度周日</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+      <c r="I73" s="3" t="n"/>
+      <c r="J73" s="3" t="n"/>
+    </row>
+    <row r="74" ht="52" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>10/11 (周日)</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>首尔 (SEL)</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>岛山公园潮流地标巡礼 (HAUS DOSAN / London Bagel)</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>深度打卡岛山公园周边先锋商业矩阵。
-• HAUS DOSAN：Gentle Monster 六层概念零售空间、TAMBURINS 艺术香氛、NuDake 黑色熔岩牛角包艺术甜品
-• London Bagel Museum 岛山店英伦复古红砖门头留影</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>🚶 沿狎鸥亭罗德奥街漫步即达岛山公园南侧</t>
-        </is>
-      </c>
-      <c r="J73" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="36" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>Day 9</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>10/10 (周六)</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>London Bagel Museum (安国店抢先取号)</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>清晨从酒店轻松步行至安国店。08:00 准时在门前现场平板扫码取号（CatchTable 等位系统），锁定心仪的葱花奶油芝士贝果与松露贝果。取号后完全无需原地干等，从容开启清幽人少的北村晨拍！</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>当天 08:00 到店平板取号，候补期间游览北村与景福宫，时间丝毫不浪费</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>🚶 从九树酒店向北步行仅 5 分钟直达安国店</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>周日早晨 08:00 取号排号靠前，通常在 09:30-10:00 即可入座或打包外带。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="52" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>10/11 (周日)</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>首尔 (SEL)</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>名人里脊 (Myeongin Deungsim) 1++ 韩牛盛宴</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>本次首尔行程最重磅的美食巅峰！全首尔公认最高水准的 1++ BMS No.9 顶级纯血熟成韩牛专卖店。全程由资深老师傅炭火代烤，肉汁在口中爆开如同雪花融化。</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>🥩 必点传奇神品：特选熟成 1++ 里脊牛排 (Special Aged Sirloin)、大理石纹雪花里脊、大蒜牛骨炒饭、韩式大酱汤</t>
-        </is>
-      </c>
-      <c r="H74" s="7" t="inlineStr">
-        <is>
-          <t>📌 建议提前请酒店礼宾部或电话协助确认座位</t>
-        </is>
-      </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>🚶 从岛山公园步行 3 分钟即达 53 Eonju-ro 172-gil</t>
-        </is>
-      </c>
-      <c r="J74" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="36" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>Day 9</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>10/10 (周六)</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>北村韩屋村桂洞晨拍 &amp; Cafe del cotone 小憩</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>穿入桂洞与嘉会洞石板坡道。清晨无游人打扰，传统青瓦木梁民居在初秋薄雾晨光中静谧典雅；漫步至胡同尽头的 Cafe del cotone（棉花主题治愈系咖啡小店），品尝温润绵柔的云朵拿铁与棉花特调 Flat White。</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>☕ Cafe del cotone：招牌 Cotone Cloud Latte、香草海盐焦糖拿铁</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>🚶 从 London Bagel 沿桂洞路向北漫步 4 分钟即达</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>北村为传统居民住宅区，清晨游览请轻声漫步；站在坡顶可远眺首尔现代摩天高楼与古建屋檐同框大片。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="52" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>10/11 (周日)</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>首尔 (SEL)</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>狎鸥亭现代百货夜景 ➔ 回酒店休息</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>晚餐后在狎鸥亭感受江南璀璨夜景，搭乘出租车越过东湖大桥返回九树仁寺洞酒店休息。</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>🚕 狎鸥亭打车返回钟路九树酒店约 20 分钟</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Day 10 · 10/11 (周日) ｜ 西村晨咖 ➔ 景福宫韩服 ➔ 土俗村参鸡汤 ➔ 北村桂洞小巷 ➔ MMCA 现代美术馆 ➔ 仁寺洞人人 ➔ 📌 On 6.5 泡菜餐酒馆 ｜ 🏨 酒店：Nine Tree Premier Hotel Insadong ｜ ☀️ 首尔日落 17:58 ｜ 🏛️ 传统人文与新派美学：宫阙秋韵、传统韩屋、米其林创意泡菜餐酒</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
-      <c r="H76" s="3" t="n"/>
-      <c r="I76" s="3" t="n"/>
-      <c r="J76" s="3" t="n"/>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>北村买手雅集 (Le Labo 北村韩屋店 ➔ Tout Y Est 北村旗舰店)</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>探访北村两座极富设计美学的地标旗舰：
+• Le Labo 北村韩屋店：罕见的古建韩屋概念香氛体验店，阳光透过传统韩纸格窗洒在木梁柱上，现场调香体验独一无二；
+• Tout Y Est 北村旗舰店：韩国小众复古高级皮具包袋美学馆，木质展柜陈列经典锁扣包与随身小皮件。</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>🚶 沿北村三清洞方向小径漫步 3 分钟即达</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>两家店的陈列均与周围古朴街景完美相融，极具东方禅意与精致法风。</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
@@ -4214,22 +4236,22 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>西村小巷漫步 &amp; Camel Coffee (西村店)</t>
+          <t>景福宫 (Gyeongbokgung Palace) 皇家宫阙漫游</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>清晨探访景福宫西侧充满质朴人文气息的西村。避开游人，在韩屋改建的 Camel Coffee 西村店露台享用招牌复古特调维也纳咖啡。</t>
+          <t>穿过三清洞来到朝鲜五大宫阙之首景福宫。游览光化门、勤政殿、庆会楼与香远亭，漫步金秋银杏古道。身着传统韩服可免门票直接入宫参观！</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>☕ 必喝：Camel Coffee 招牌浓厚坚果奶香冰咖啡</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
@@ -4239,12 +4261,12 @@
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>🚶 从九树酒店向西漫步 10 分钟穿过光化门广场即达西村</t>
+          <t>🚶 从北村向西穿过三清洞马路，步行 5 分钟直达景福宫神武门/建春门</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>庆会楼水上倒影与香远亭池塘是拍摄古典大片的绝对机位。</t>
         </is>
       </c>
     </row>
@@ -4266,419 +4288,441 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>午餐：土俗村参鸡汤 (Tosokchon Samgyetang)</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>走出景福宫迎秋门来到韩国公认第一的传奇老店土俗村。在古色古香的传统韩屋四合院内，品尝整只童子鸡塞满高丽参、板栗、糯米熬煮至骨肉酥烂的极品浓白鸡汤！</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>🍲 传奇滋补美味：特选山参参鸡汤 + 海鲜葱饼配脆爽辣萝卜泡菜</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>🚶 从景福宫西门沿紫霞门路步行 4 分钟即达</t>
+        </is>
+      </c>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>12:00 前到达排队极快，浓汤热气腾腾极度温润滋补。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="52" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>10/11 (周日)</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>首尔 (SEL)</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>西村文艺慢步 (ofr Seoul ➔ little tempo ➔ one more bag ➔ regins)</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>步入充满生活气息与人文烟火气的西村（Seochon）：
+• ofr Seoul：巴黎知名独立书店首尔分店，两层复古老洋房，淘选艺术画册、经典帆布袋与复古饰品；
+• little tempo：治愈系插画文创杂货小铺，选购可爱卡通生活周边；
+• one more bag：原创设计师布包集合店，琳琅满目的趣味挂件与环保布袋；
+• regins：探访西村极具品味的手作生活器物与选品杂货。</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>🚶 沿通仁洞与玉仁洞街道一路漫步探店</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>西村没有明洞的喧闹，保留了首尔最质朴亲切的胡同温情，适合放慢脚步细细淘宝。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="52" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>10/11 (周日)</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>首尔 (SEL)</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>西村下午茶享受 (PHAL / Camel Coffee 西村店 / Namusae 韩屋茶室)</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>在西村选择一家心仪的感性咖啡馆歇脚放空：
+• PHAL：质感设计极简咖啡空间；
+• Camel Coffee 西村店：老旧木质韩屋改建，招牌浓郁坚果奶香冰咖啡；
+• Namusae Tea House (韩屋茶室)：坐在传统木质走廊下，品尝传统五味子茶、大枣茶与软糯传统打糕。</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>🍵 传统茶歇：Namusae 冰镇五味子茶 + 烤蜂蜜韩菓年糕</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>🚶 均分布在西村与通义洞胡同内，步行即达</t>
+        </is>
+      </c>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>韩屋庭院静谧安详，秋日下午阳光斑驳，享受悠闲下午时光。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="52" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>10/11 (周日)</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>首尔 (SEL)</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>晚餐经典四选一：神洞宫土豆脊骨汤 / 两门烤肉 / 武桥洞干明太鱼汤 / 元祖马山安康鱼</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>根据手绘图推荐，在酒店周边享用首尔经典老字号晚餐：
+• 选项一 (首推)：Sindonggung 神洞宫 (乙支路店) 炭烤辣脊骨与浓郁土豆排骨汤；
+• 选项二：两门烤肉 (남영동양문) 炭火鲜烤特大排骨配特制水冷面；
+• 选项三：武桥洞干明太鱼汤 (Mugyodong Bugeokukjib) 醇浓解腻传统暖汤饭；
+• 选项四：元祖马山辣炖安康鱼。
+餐后漫步清溪川夜步，返回酒店整理行装。</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>🍲 首推美味：神洞宫炭火烤辣排骨 (Spicy Pork Bone BBQ) + 浓白骨汤</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>🚶 从西村步行或乘出租车 5-8 分钟返回钟路/乙支路美食商圈</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>四家店都在九树酒店步行 5-10 分钟范围内，吃完散步回酒店极度省心无负担。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Day 11 · 10/12 (周一) ｜ 首尔林森林漫步(Milestone咖啡/红袍核桃) ➔ 陵洞水芹菜牛骨汤饭 ➔ 圣水洞先锋买手(Amuse/Point of View/Tamburins/GM HQ/Miffy/Stand Oil/Low Classic/LCDC) ➔ Maman Gelato/Jayeondo盐面包 ➔ 取行李 ➔ AREX ➔ 仁川T1返程 ｜ 🏨 酒店：仁川机场 T1 / 跨洋返程客机 ｜ ☀️ 首尔日落 17:57 ｜ ✈️ 完美收官日：周一圣水洞错峰避人流，首尔林自然森呼吸 + 圣水先锋买手全收录</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n"/>
+      <c r="C82" s="3" t="n"/>
+      <c r="D82" s="3" t="n"/>
+      <c r="E82" s="3" t="n"/>
+      <c r="F82" s="3" t="n"/>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+      <c r="I82" s="3" t="n"/>
+      <c r="J82" s="3" t="n"/>
+    </row>
+    <row r="83" ht="52" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>10/12 (周一)</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>首尔 (SEL)</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>景福宫韩服沉浸体验 (Gyeongbokgung Palace)</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>在景福宫门前租赁精致宫廷韩服（身着韩服免门票直接入宫！）。漫步于勤政殿、庆会楼水上倒影殿宇与香远亭，在初秋金黄银杏叶下拍摄古典古装大片。</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="7" t="inlineStr">
-        <is>
-          <t>穿着韩服免门票入宫；周日注意避开拥挤人群早入宫拍照</t>
-        </is>
-      </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>🚶 从西村步行 3 分钟即达景福宫迎秋门/光化门</t>
-        </is>
-      </c>
-      <c r="J78" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="36" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>Day 10</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>10/11 (周日)</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>首尔林森林漫步 &amp; Milestone Coffee (首尔林店)</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>特意将圣水洞与首尔林安排在周一！人流比周末骤降 70%，漫步体验极其清幽。清晨步入首尔林公园，在挺拔的水杉林荫道与中央湖畔漫步森呼吸；随后前往邻近的 Milestone Coffee 首尔林店，品尝招牌维也纳咖啡与手绘图特别标注的「红袍核桃磅蛋糕」！</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>☕ 招牌晨点：Milestone Vienna Coffee (手打厚鲜奶油冰咖啡) + 红袍核桃磅蛋糕 (Walnut Pound Cake)</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>🚇 酒店退房后行李暂存前台，乘 3 号线至新沙转水仁盆唐线至首尔林站 (Seoul Forest) 5 号出口（约 25 分钟）</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>首尔林秋色宜人，微风拂面；Milestone 09:30 开门即可入座，无需周末长队等待。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="52" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>10/12 (周一)</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>首尔 (SEL)</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>土俗村参鸡汤 (Tosokchon Samgyetang)</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>韩国总统同款、全韩公认第一的传奇参鸡汤老店！古色古香的传统韩屋四合院内，整只童子鸡塞满糯米、高丽人参、栗子、红枣、南瓜籽熬煮至酥烂浓郁。</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>🍲 必点美味：特选山参参鸡汤 (Mountain Ginseng Samgyetang)、海鲜葱饼配脆爽辣萝卜泡菜</t>
-        </is>
-      </c>
-      <c r="H79" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>🚶 从景福宫西门向西步行 4 分钟即达</t>
-        </is>
-      </c>
-      <c r="J79" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="36" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>Day 10</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>10/11 (周日)</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>午餐：陵洞水芹菜 (Neungdong Minari 圣水店)</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>步入圣水洞当下最爆火的特色美食店陵洞水芹菜。品尝热气腾腾的招牌水芹菜牛骨汤饭——鲜嫩大块牛腱肉与牛骨高汤中铺满鲜嫩清香的当季绿色水芹菜，汤汁清甜鲜爽绝不油腻；搭配招牌水芹菜生拌牛肉与鲜辣萝卜，令人食指大动！</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>🍲 招牌午餐：水芹菜牛骨牛肉汤饭 (Minari Beef Gomtang) + 水芹菜生拌牛肉</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>🚶 从首尔林向圣水站方向漫步 8 分钟即达</t>
+        </is>
+      </c>
+      <c r="J84" s="7" t="inlineStr">
+        <is>
+          <t>周一中午避开周末两小时等位，水芹菜清香与醇香牛骨汤是绝配，吃完全身暖洋洋。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="52" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>10/12 (周一)</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>首尔 (SEL)</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>北村韩屋村桂洞小巷 (Bukchon Hanok Village)</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>穿过安国来到北村桂洞与嘉会洞。站在石板斜坡顶端远眺青瓦木梁传统屋檐与远方首尔塔、现代摩天大楼重叠的经典风光。</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>🚶 从景福宫向东穿过三清洞步行 10 分钟至北村</t>
-        </is>
-      </c>
-      <c r="J80" s="7" t="inlineStr">
-        <is>
-          <t>北村为居民生活区，游览请保持轻声细语</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="36" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>Day 10</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>10/11 (周日)</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>圣水洞先锋买手与文创殿堂巡礼 (Amuse ➔ Point of View ➔ Tamburins ➔ GM HQ ➔ Miffy ➔ Stand Oil ➔ Low Classic ➔ LCDC)</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>午后深度探索圣水洞各大标志性美学旗舰：
+• AMUSE 圣水概念展厅：张元英同款纯素彩妆，马卡龙色系空间体验水光果冻唇釉；
+• Point of View 圣水：全球公认顶级独立文创纸品文具神殿，三层复古洋房，陈列高品质手账本、黄铜镇纸与独立艺术周边；
+• Tamburins 圣水：下沉式清水混凝土巨型香氛艺术馆；
+• GM HQ (HAUS NOWHERE 圣水)：Gentle Monster 超级未来概念全球总部，打卡巨型机械动力装置；
+• Miffy Store：可爱米菲兔首尔概念专卖店；
+• STAND OIL 圣水旗舰：火爆全网的经典百搭保龄球包手袋店；
+• LOW CLASSIC 圣水旗舰：韩国极简冷淡风设计师女装；
+• LCDC Seoul：集合时尚、艺术书籍与家居买手的复合空间。</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>🚶 沿 Yeonmujang-gil（演武场街）与成水二路一路漫步逛街</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>所有品牌旗舰店均集中在方圆 500 米内，周一逛店非常从容，购物直接在收银台退税。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="52" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Day 11</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>10/12 (周一)</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>首尔 (SEL)</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>Cafe Del Cotone (北村桂洞棉花咖啡)</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>藏匿在桂洞胡同尽头的棉花主题治愈系小店。纯白织物与复古木窗，品尝如云朵般轻柔细腻的招牌棉花拿铁与手工磅蛋糕。</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr">
-        <is>
-          <t>☕ 招牌：Cotone Cloud Latte、香草海盐焦糖拿铁</t>
-        </is>
-      </c>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>🚶 桂洞街道旁步行 2 分钟</t>
-        </is>
-      </c>
-      <c r="J81" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="36" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>Day 10</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>10/11 (周日)</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>首尔 (SEL)</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>国立现代美术馆首尔馆 (MMCA Seoul)</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>打卡融合传统红砖与极简清水混凝土的艺术殿堂。漫步中央艺术草坪与当代多媒体先锋展厅，感受首尔年轻艺术家的澎湃创意。</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>门票 5,000 韩元（或部分展期免费）</t>
-        </is>
-      </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>🚶 从桂洞向西漫步 5 分钟即达昭格洞 MMCA</t>
-        </is>
-      </c>
-      <c r="J82" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="36" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>Day 10</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>10/11 (周日)</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>首尔 (SEL)</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>仁寺洞人人商场 (Ssamziegil) 文创艺术街</t>
-        </is>
-      </c>
-      <c r="F83" s="7" t="inlineStr">
-        <is>
-          <t>漫步于螺旋上升式的无台阶创意手作回旋街。打卡 Acorn Caricature 橡子漫画人像快画馆（一分钟手绘复古暖心漫画头像，旅途最佳纪念品）。</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J83" s="7" t="inlineStr">
-        <is>
-          <t>⭐ 纪念必打卡：画一张专属首尔旅途手绘漫画头像！</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="36" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Day 10</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>10/11 (周日)</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>首尔 (SEL)</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>On 6.5 (米其林推荐现代泡菜创意餐酒馆)</t>
-        </is>
-      </c>
-      <c r="F84" s="7" t="inlineStr">
-        <is>
-          <t>本次首尔之旅最具创意的美食体验！以韩国灵魂“泡菜在 6.5℃ 下发酵最完美”为灵感的高级概念餐酒馆，将传统发酵艺术升华至米其林星级水准。</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>🍷 必尝创意大作：泡菜炸紫菜卷佐手工酸奶油、东海鲍鱼海苔烩饭、泡菜香炸排骨配自然橙酒</t>
-        </is>
-      </c>
-      <c r="H84" s="7" t="inlineStr">
-        <is>
-          <t>📌 必须提前通过 CatchTable 预约 18:30 晚餐时段，入店需点佐餐酒水</t>
-        </is>
-      </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>🚶 位于安国站 1 号出口旁，从人人商场步行 4 分钟即达</t>
-        </is>
-      </c>
-      <c r="J84" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="36" customHeight="1">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>Day 10</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>10/11 (周日)</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>首尔 (SEL)</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>Olive Young (钟路/安国店) 补货 ➔ 回酒店</t>
-        </is>
-      </c>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>晚餐后轻松散步，最后采购心仪的护肤面膜与伴手礼，步行 3 分钟悠闲返回九树酒店整理行李。</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H85" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>🚶 步行 3 分钟返回九树酒店</t>
-        </is>
-      </c>
-      <c r="J85" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Day 11 · 10/12 (周一) ｜ ⭐ 圣水洞全天潮流探索 ➔ Dior 梦幻宫殿 ➔ 祖传三代排骨汤 ➔ 取行李 ➔ AREX 直通 ➔ 仁川 T1 贵宾室 ➔ 返程 ｜ 🏨 酒店：仁川机场 T1 / 跨洋返程客机 ｜ ☀️ 首尔日落 17:57 ｜ ✈️ 完美收官日：周一圣水洞人少清幽，深度扫街，从容奔赴机场返航</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="n"/>
-      <c r="C86" s="3" t="n"/>
-      <c r="D86" s="3" t="n"/>
-      <c r="E86" s="3" t="n"/>
-      <c r="F86" s="3" t="n"/>
-      <c r="G86" s="3" t="n"/>
-      <c r="H86" s="3" t="n"/>
-      <c r="I86" s="3" t="n"/>
-      <c r="J86" s="3" t="n"/>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>甜品能量补给：Maman Gelato ➔ Jayeondo 自然岛盐面包</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>在离开圣水洞前品尝两款现象级口碑甜品：
+• Maman Gelato：品尝天然水果与坚果手工打制的纯正意式 Gelato 冰淇淋；
+• 自然岛盐面包 (Jayeondo)：买上一袋刚出炉的海盐黄油面包，热气腾腾底部焦脆，浓郁黄油香与海盐微咸交织，香脆松软无比绝妙！</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>🥐 Jayeondo 刚出炉盐面包 (四只一包装) + Maman Gelato 手工冰淇淋</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>🚶 位于演武场街主街旁，步行 2 分钟即达</t>
+        </is>
+      </c>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>盐面包现场每半小时出炉一锅，出炉趁热撕开品尝口感最巅峰，亦可带上飞机作为下午茶！</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
@@ -4698,17 +4742,17 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>圣水洞晨间艺术探索 (Seongsu-dong)</t>
+          <t>返回九树仁寺洞酒店提取寄存行李</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>特意将圣水洞安排在周一！完美避开周末排队几小时的恐怖人流。漫步在红砖工业老厂房改建的街区，感受首尔“布鲁克林”独特的工业废土与前卫美学碰撞。</t>
+          <t>搭乘出租车或地铁返回仁寺洞九树酒店，前台提取上午寄存的行李箱，在大堂将圣水洞战利品与伴手礼从容打包归纳整齐。</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
@@ -4723,7 +4767,7 @@
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>🚇 酒店乘地铁 3 号线转 2 号线至圣水站 3/4 号出口（约 20 分钟）</t>
+          <t>🚕 圣水洞打车返回九树酒店（车程约 18 分钟，约 12,000 韩元），省心快捷</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
@@ -4750,22 +4794,22 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Camel Coffee (圣水 7 号店) / 大林仓库</t>
+          <t>首尔站搭乘 AREX 直通特急 ➔ 仁川机场 T1 / 离境返程</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>在老旧皮革厂房改造的 Camel Coffee 圣水店或大林仓库（Daelim Changgo）高挑挑空厂房内，品味醇厚浓缩咖啡与香酥羊角包，欣赏红砖墙上的大型当代艺术装置。</t>
+          <t>前往首尔站搭乘 AREX 机场直通特急列车，一站直达仁川国际机场第一航站楼（T1，用时仅 43 分钟，避开晚高峰地面塞车）。在机场自助退税机退税，办理航班值机与托运，步入 Sky Hub 贵宾休息室休整，搭乘国际航班平安圆满归家！</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>☕ 招牌推荐：Camel Coffee 特调冰咖啡、可颂牛角包</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -4775,435 +4819,12 @@
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>🚶 圣水站 3 号出口步行 4 分钟</t>
+          <t>🚆 AREX 机场特急直通列车（直达 T1 约 43 分钟）</t>
         </is>
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="52" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>Day 11</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>10/12 (周一)</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>首尔 (SEL)</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>Dior 圣水概念宫殿 &amp; HAUS NOWHERE &amp; TAMBURINS</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>打卡圣水洞三大地标级视觉建筑。
-• Dior 圣水（梦幻透明玻璃温室法式宫殿外观拍照）
-• HAUS NOWHERE SEOUL（Gentle Monster 圣水超级未来概念旗舰，巨型人形机器人与艺术陈列）
-• TAMBURINS 圣水（下沉式清水混凝土清水地下香氛艺术空间）</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>🚶 沿 Yeonmujang-gil（演武场街）一路漫步打卡</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="36" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>Day 11</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>10/12 (周一)</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>首尔 (SEL)</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>传说的圣水土豆排骨汤 (Somunnan Gamjatang)</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>全首尔排队最火爆的祖传三代老字号排骨汤！避开周末长队，周一中午从容品尝。超大块猪脊骨炖煮至骨肉自然分离，汤底醇厚香浓带着白苏籽香气。</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>🍲 必吃美味：招牌猪脊骨土豆汤、苏子叶土豆排骨、最后必加炒饭与拉面</t>
-        </is>
-      </c>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>🚶 从演武场街步行 3 分钟即达</t>
-        </is>
-      </c>
-      <c r="J90" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="52" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>Day 11</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>10/12 (周一)</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>首尔 (SEL)</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>圣水潮牌最终扫货 (Musinsa / Rockfish / Stand Oil)</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>午后抓紧最后时光采购圣水洞限定好物。
-• Musinsa Standard 圣水超大多层旗舰店
-• Rockfish Weatherwear 圣水（英伦雨靴与芭蕾鞋）
-• STAND OIL（经典百搭保龄球包）
-• Olive Young N Seongsu（首尔最新五层科技旗舰店）补齐最后的退税好物</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H91" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J91" s="7" t="inlineStr">
-        <is>
-          <t>采购完毕后检查退税单是否齐全，以便在机场快捷退税</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="36" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>Day 11</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>10/12 (周一)</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>首尔 (SEL)</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>返回九树酒店提取寄存行李</t>
-        </is>
-      </c>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>搭乘地铁或出租车返回仁寺洞九树酒店，在大堂整理全部战利品与打包箱，前台提取寄存行李。</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>🚕 圣水洞打车回酒店约 18 分钟</t>
-        </is>
-      </c>
-      <c r="J92" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="36" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>Day 11</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>10/12 (周一)</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>首尔 (SEL)</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>首尔站搭乘 AREX 直通列车 ➔ 仁川 T1</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>前往首尔站搭乘 AREX 机场直通特急列车，一站直达仁川国际机场第一航站楼（T1，用时仅约 43 分钟，舒适准时且避开晚高峰地面塞车）。</t>
-        </is>
-      </c>
-      <c r="G93" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>🚆 AREX 机场特急直通列车（直达 T1 约 43 分钟）</t>
-        </is>
-      </c>
-      <c r="J93" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="36" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>Day 11</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>10/12 (周一)</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>首尔 (SEL)</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>仁川国际机场 T1 航站楼值机与退税</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>抵达仁川 T1，在自助退税机扫描退税单与护照，办理航班值机托运行李手续，快速通过安检与出境审查，在航站楼内领取退税现金。</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="inlineStr">
-        <is>
-          <t>仁川机场 T1 免税店众多，安检后可在 28 号登机口附近领取退税现金</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="36" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>Day 11</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>10/12 (周一)</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>首尔 (SEL)</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>仁川 T1 Sky Hub / Matina 贵宾休息室休整</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>在登机前步入 T1 优质贵宾休息室。冲凉洗漱更换舒适的飞行长裤，享用热腾腾的韩式拌饭、辛拉面、果汁与美酒，回顾 11 天美韩金秋梦幻旅程。</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>🍜 休息室美食：现煮韩式辛拉面、自助石锅拌饭、新鲜水果配红白葡萄酒</t>
-        </is>
-      </c>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I95" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J95" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="36" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>Day 11</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>10/12 (周一)</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>首尔 (SEL)</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>搭乘返程航班起飞 ➔ 圆满平安归家</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>搭乘深夜国际航班平稳起飞。满载难忘的美好回忆、艺术灵感与丰厚战利品，为本次 2026 纽约·首尔深度优化旅行画上完美句号！</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I96" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J96" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>AREX 直通特急准时高效；提前在 T1 28 号登机口附近领取退税现金。</t>
         </is>
       </c>
     </row>
@@ -5216,9 +4837,9 @@
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A57:J57"/>
+    <mergeCell ref="A73:J73"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A86:J86"/>
-    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="A82:J82"/>
     <mergeCell ref="A51:J51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6097,7 +5718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7189,6 +6810,326 @@
       <c r="H27" s="7" t="inlineStr">
         <is>
           <t>⚠️ 易斯达为廉航，机上餐食需付费，建议在休息室吃饱再登机</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>首尔</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>汉南洞</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>经典韩式部队锅暖心午餐（10/09 周五 13:00）</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Hannam Budaejjigae 汉南部队锅</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>特制双份芝士部队锅 (Budae Jjigae) + 农心辛拉面组合</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Solgot Hannam (汉南洞精致传统釜饭)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>汉南洞多年老饕排队名店，牛骨浓汤、午餐肉与芝士辛拉面，全天漫步最佳能量补给。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>首尔</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>汉南洞</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>首尔顶级法式奢华烘焙下午茶（10/09 周五 15:30）</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Passion 5 奢华甜品宫殿</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>草莓鲜奶油蛋糕 / 招牌香草千层酥 (Mille-feuille) + 现磨手冲黑咖啡</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Oasis Cafe (汉南洞绿植花园庭院早午餐咖啡)</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>首尔天花板级甜品艺术馆，水滴旋转楼梯极具仪式感。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>首尔</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>江南新沙</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>新沙洞酱蟹老字号巅峰晚宴（10/10 周六 18:00）</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>元祖马山辣炖安康鱼 &amp; 酱蟹老店</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>顶级满黄特大酱油腌蟹 (Ganjang Gejang) + 辣炖安康鱼 (Agujjim) + 蟹黄拌饭</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>PRO 酱蟹 (新沙总店)</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>新沙洞酱蟹一条街鼻祖老字号，蟹肉晶莹剔透，浓醇蟹黄拌饭绝品美味。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>首尔</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>西村 / 景福宫</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>韩国第一高丽参童子鸡滋补午餐（10/11 周日 12:00）</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>土俗村参鸡汤 (Tosokchon Samgyetang)</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>特选山参参鸡汤 (Mountain Ginseng Samgyetang) + 海鲜葱饼配脆爽辣萝卜</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>百年参鸡汤 (北村店)</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>韩国总统同款老店，古色古香韩屋院落内享用整只童子鸡塞满高丽参糯米浓汤。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>首尔</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>乙支路 / 钟路</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>炭火鲜烤特大排骨经典晚餐（10/11 周日 18:00）</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>两门烤肉 (남영동양문 乙支路店)</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>炭火鲜烤牛大排骨 (Grilled Beef Ribs) + 附赠特制牛骨汤与大水冷面</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>神洞宫炭火脊骨汤 (乙支路店)</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>老首尔市井排队烤肉王，炭烤肉香四溢，赠送的骨汤与冷面超值过瘾。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>首尔</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>市厅 / 清溪川</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>1968年开业至今的老首尔神级暖汤（10/11 周日 晚餐备选）</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>武桥洞干明太鱼汤 (Mugyodong Bugeokukjib)</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>纯厚浓白明太鱼汤饭 (Bugeokuk) + 腌虾酱与手工葱泡菜</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>清进屋牛血解酒汤</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>半个世纪只专注熬制一碗极致浓醇的明太鱼汤，鲜甜暖胃，老首尔市井灵魂。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>首尔</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>圣水洞</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>鲜爽水芹菜牛骨汤饭暖心午餐（10/12 周一 11:45）</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>陵洞水芹菜 (Neungdong Minari 圣水店)</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>水芹菜牛骨牛肉汤饭 (Minari Beef Gomtang) + 水芹菜生拌牛肉</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>传说的圣水土豆排骨汤</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>圣水洞当下最爆火餐厅，大块牛腱肉搭配铺满的当季鲜爽绿色水芹菜，清甜解腻。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>首尔</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>圣水洞</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>现象级出炉焦脆咸香黄油面包（10/12 周一 15:30 甜点）</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>自然岛盐面包 (Jayeondo Salt Bread 圣水店)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>现烤海盐黄油盐面包 (刚出炉四包装) + Maman Gelato 手工冰淇淋</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Standard Bread 手撕生吐司</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>首尔排队最长盐面包名店，外壳焦脆内部黄油爆汁微咸，趁热吃堪称巅峰享受。</t>
         </is>
       </c>
     </row>
